--- a/assets/files/hul-business-model.xlsx
+++ b/assets/files/hul-business-model.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'CF'!$A$2:$G$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Key Ratios'!$A$2:$G$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'DCF Model'!$A$2:$K$80</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'PE Valuation'!$A$2:$K$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'PE Valuation'!$A$1:$K$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Football Field'!$A$2:$R$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -48,7 +48,7 @@
     <numFmt numFmtId="176" formatCode="\₹#,##0;&quot;(₹&quot;#,##0\);\-"/>
     <numFmt numFmtId="177" formatCode="\+0.00%;\-0.00%;0.00%"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -354,8 +354,15 @@
       <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -396,6 +403,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9DEF5"/>
         <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,7 +459,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1173,6 +1185,8 @@
     <xf numFmtId="1" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2123,7 +2137,7 @@
     <row r="4" ht="24.75" customHeight="1" s="122">
       <c r="B4" s="127" t="inlineStr">
         <is>
-          <t>All figures in ₹ Millions (INR Mn) unless otherwise stated | Updated: 14 Jul 2026</t>
+          <t>All figures in ₹ Millions (INR Mn) unless otherwise stated | Updated: 21 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2268,7 @@
       </c>
       <c r="D22" s="140" t="inlineStr">
         <is>
-          <t>vs. ₹2,130</t>
+          <t>vs. ₹2,140</t>
         </is>
       </c>
       <c r="E22" s="140" t="inlineStr">
@@ -2392,7 +2406,7 @@
       </c>
       <c r="C37" s="151" t="inlineStr">
         <is>
-          <t>Use DCF as a discipline check, not a target. The implied ~9.1% terminal growth is aggressive for a mature FMCG franchise. A blended view (70% P/E, 30% DCF) gives a fair value of ~₹2,190 — essentially in line with the market price of ₹2,130. Rating: HOLD (no margin of safety at current levels; quality intact).</t>
+          <t>Use DCF as a discipline check, not a target. The implied ~9.1% terminal growth is aggressive for a mature FMCG franchise. A blended view (70% P/E, 30% DCF) gives a fair value of ~₹2,190 — essentially in line with the market price of ₹2,140. Rating: HOLD (no margin of safety at current levels; quality intact).</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5410,7 @@
         </is>
       </c>
       <c r="C17" s="242" t="n">
-        <v>2130</v>
+        <v>2139.7</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="122">
@@ -6283,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K37"/>
+  <dimension ref="A2:K68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="121" min="1" max="1"/>
@@ -6703,9 +6717,154 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="243" t="inlineStr">
+        <is>
+          <t>ADDITIONAL VALUATION CROSS-CHECKS (multi-method)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="244" t="inlineStr">
+        <is>
+          <t>DIVIDEND DISCOUNT MODEL (H-model, 2-stage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="121" t="inlineStr">
+        <is>
+          <t>FY26 dividend per share (₹)</t>
+        </is>
+      </c>
+      <c r="B53" s="121" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="121" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B54" s="121" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="121" t="inlineStr">
+        <is>
+          <t>Near-term dividend growth (gS, 5y)</t>
+        </is>
+      </c>
+      <c r="B55" s="121" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="121" t="inlineStr">
+        <is>
+          <t>Terminal growth (gL)</t>
+        </is>
+      </c>
+      <c r="B56" s="121" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="121" t="inlineStr">
+        <is>
+          <t>H (half of high-growth years)</t>
+        </is>
+      </c>
+      <c r="B57" s="121" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="121" t="inlineStr">
+        <is>
+          <t>DDM value = [D0(1+gL)+D0·H·(gS−gL)]/(Ke−gL) (₹)</t>
+        </is>
+      </c>
+      <c r="B58" s="121">
+        <f>(B53*(1+B56)+B53*B57*(B55-B56))/(B54-B56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="244" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="121" t="inlineStr">
+        <is>
+          <t>FY26 EBITDA (₹ Mn)</t>
+        </is>
+      </c>
+      <c r="B62" s="121">
+        <f>IS!G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="121" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA (x) — vs ~33x current</t>
+        </is>
+      </c>
+      <c r="B63" s="121" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="121" t="inlineStr">
+        <is>
+          <t>Enterprise value (₹ Mn)</t>
+        </is>
+      </c>
+      <c r="B64" s="121">
+        <f>B62*B63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="121" t="inlineStr">
+        <is>
+          <t>Add: net cash (₹ Mn)</t>
+        </is>
+      </c>
+      <c r="B65" s="121" t="n">
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="121" t="inlineStr">
+        <is>
+          <t>EV/EBITDA-implied value / share (₹)</t>
+        </is>
+      </c>
+      <c r="B66" s="121">
+        <f>(B64+B65)/IS!G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="121" t="inlineStr">
+        <is>
+          <t>Note: DDM (~₹1,034) and EV/EBITDA (~₹1,928) sit between the cash-flow DCF (₹712) and the relative P/E (₹2,826) — HUL's quality premium shows up only in the multiple-based methods. Blended target unchanged at ~₹2,190 (HOLD).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="B2:K2"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6747,12 +6906,12 @@
     <row r="3" ht="15" customHeight="1" s="122">
       <c r="B3" s="233" t="inlineStr">
         <is>
-          <t>Implied share price range by valuation methodology | Current price: ₹2,350</t>
+          <t>Implied share price range by valuation methodology | Current price: ₹2,140</t>
         </is>
       </c>
       <c r="D3" s="121" t="inlineStr">
         <is>
-          <t>Implied share price range by valuation methodology | Current price: ₹2,130</t>
+          <t>Implied share price range by valuation methodology | Current price: ₹2,140</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6998,7 @@
         <v/>
       </c>
       <c r="H7" s="237" t="n">
-        <v>2130</v>
+        <v>2139.7</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="122">
@@ -6905,13 +7064,13 @@
         </is>
       </c>
       <c r="C10" s="240" t="n">
-        <v>2100</v>
+        <v>2023</v>
       </c>
       <c r="D10" s="241" t="n">
-        <v>2350</v>
+        <v>2139.7</v>
       </c>
       <c r="E10" s="240" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="F10" s="235">
         <f>E10-C10</f>
